--- a/data/trans_orig/P6714-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6714-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se sienten comprometidos con su profesión en 2012</t>
+          <t>Población según si se sienten comprometidos con su profesión en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14276</t>
+          <t>15732</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13537</t>
+          <t>13447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20464</t>
+          <t>20746</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>38642</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>13710</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30491</t>
+          <t>30930</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36942</t>
+          <t>36230</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63693</t>
+          <t>62478</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55361</t>
+          <t>55310</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84573</t>
+          <t>83777</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36415</t>
+          <t>37272</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60001</t>
+          <t>61118</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96792</t>
+          <t>97625</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134683</t>
+          <t>135616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>144664</t>
+          <t>143796</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176557</t>
+          <t>176290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72410</t>
+          <t>70687</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>98853</t>
+          <t>97204</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>225233</t>
+          <t>225478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>266180</t>
+          <t>266999</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,06%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12431</t>
+          <t>12827</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17915</t>
+          <t>18332</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20597</t>
+          <t>20027</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>18230</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12881</t>
+          <t>12718</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32505</t>
+          <t>33785</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43723</t>
+          <t>45711</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73741</t>
+          <t>75088</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39548</t>
+          <t>39945</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67902</t>
+          <t>67752</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91388</t>
+          <t>91083</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131905</t>
+          <t>131674</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71541</t>
+          <t>72325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105778</t>
+          <t>106509</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50359</t>
+          <t>51285</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79606</t>
+          <t>80083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129581</t>
+          <t>128678</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>174868</t>
+          <t>176343</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>225043</t>
+          <t>225462</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>267210</t>
+          <t>266445</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123227</t>
+          <t>120069</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156010</t>
+          <t>155742</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>360671</t>
+          <t>359197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>415045</t>
+          <t>414356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,82%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16373</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27704</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29514</t>
+          <t>26771</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21820</t>
+          <t>22535</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48089</t>
+          <t>48503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29968</t>
+          <t>29568</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53218</t>
+          <t>54107</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43598</t>
+          <t>44498</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56949</t>
+          <t>57358</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91650</t>
+          <t>89539</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40268</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68863</t>
+          <t>68233</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40055</t>
+          <t>40028</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65721</t>
+          <t>66299</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86541</t>
+          <t>86773</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>125253</t>
+          <t>125465</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>185292</t>
+          <t>188353</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>221707</t>
+          <t>222522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>91678</t>
+          <t>94660</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>124956</t>
+          <t>124691</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>287130</t>
+          <t>289790</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>336452</t>
+          <t>337886</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,41%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14796</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>14269</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23596</t>
+          <t>24090</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10232</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27667</t>
+          <t>27495</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17686</t>
+          <t>16794</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37690</t>
+          <t>36725</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51780</t>
+          <t>52948</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>84240</t>
+          <t>83811</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37883</t>
+          <t>36997</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63990</t>
+          <t>66154</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>94335</t>
+          <t>96341</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>138251</t>
+          <t>137098</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>94563</t>
+          <t>95572</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>132987</t>
+          <t>130272</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60247</t>
+          <t>61223</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90488</t>
+          <t>91833</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>165006</t>
+          <t>164669</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>212705</t>
+          <t>212216</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>192425</t>
+          <t>194484</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>236879</t>
+          <t>235241</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>141454</t>
+          <t>140944</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>176139</t>
+          <t>175510</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>347821</t>
+          <t>346342</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>402635</t>
+          <t>401999</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,98%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13967</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>33441</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>28388</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29857</t>
+          <t>28500</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56367</t>
+          <t>55319</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>37093</t>
+          <t>37814</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>67962</t>
+          <t>66223</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28260</t>
+          <t>28133</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>54799</t>
+          <t>55537</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>70117</t>
+          <t>72187</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>111170</t>
+          <t>113893</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>170009</t>
+          <t>168176</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>223968</t>
+          <t>221423</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>133460</t>
+          <t>133635</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>181280</t>
+          <t>177963</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>315519</t>
+          <t>314423</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>387436</t>
+          <t>388836</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>289762</t>
+          <t>291319</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>356002</t>
+          <t>359715</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>211470</t>
+          <t>213748</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>268045</t>
+          <t>267521</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>523105</t>
+          <t>520028</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>608341</t>
+          <t>605764</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>786794</t>
+          <t>788887</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>865281</t>
+          <t>865000</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>457325</t>
+          <t>460768</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>523812</t>
+          <t>524402</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1265877</t>
+          <t>1268668</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1372103</t>
+          <t>1371607</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se sienten comprometidos con su profesión en 2016</t>
+          <t>Población según si se sienten comprometidos con su profesión en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>13774</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10914</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19452</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11172</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27013</t>
+          <t>27365</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19272</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>21251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40818</t>
+          <t>42886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28893</t>
+          <t>27577</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51805</t>
+          <t>51125</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23155</t>
+          <t>23516</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42073</t>
+          <t>43168</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56590</t>
+          <t>56911</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88465</t>
+          <t>86618</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61522</t>
+          <t>61935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90079</t>
+          <t>89370</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47129</t>
+          <t>47676</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70403</t>
+          <t>71903</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115483</t>
+          <t>115378</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152846</t>
+          <t>153241</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,32%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88173</t>
+          <t>89760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>119247</t>
+          <t>120080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49613</t>
+          <t>48226</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>74159</t>
+          <t>73392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145644</t>
+          <t>146173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>185476</t>
+          <t>185300</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,12%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15653</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,47 +5070,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5841</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2071</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12234</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5841</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12872</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>6576</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22485</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22821</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11813</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29660</t>
+          <t>30604</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23392</t>
+          <t>23500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47589</t>
+          <t>46345</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65074</t>
+          <t>64018</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100697</t>
+          <t>97267</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34701</t>
+          <t>34632</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58141</t>
+          <t>59345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107638</t>
+          <t>106781</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>148243</t>
+          <t>148617</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95487</t>
+          <t>97159</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134630</t>
+          <t>133941</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66126</t>
+          <t>65503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96823</t>
+          <t>97086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171740</t>
+          <t>170898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217035</t>
+          <t>218328</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>175609</t>
+          <t>176538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>219638</t>
+          <t>220303</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104509</t>
+          <t>105523</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138658</t>
+          <t>138314</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>295825</t>
+          <t>291876</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>347337</t>
+          <t>348490</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,67%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>23088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14173</t>
+          <t>13524</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>12432</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30894</t>
+          <t>31373</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43509</t>
+          <t>43430</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>19361</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38744</t>
+          <t>39127</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45090</t>
+          <t>44157</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75927</t>
+          <t>73283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94351</t>
+          <t>96544</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>131736</t>
+          <t>134484</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52871</t>
+          <t>53392</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81413</t>
+          <t>82239</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>158234</t>
+          <t>157347</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>201853</t>
+          <t>201658</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67606</t>
+          <t>66944</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>101169</t>
+          <t>98314</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,47 +6091,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>27,02%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>59194</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>90268</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>27,81%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>61246</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>90699</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>27,81%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135046</t>
+          <t>135709</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>177830</t>
+          <t>178317</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>106221</t>
+          <t>105640</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>141246</t>
+          <t>142148</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>79220</t>
+          <t>79466</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110786</t>
+          <t>111121</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>193786</t>
+          <t>195215</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>242227</t>
+          <t>244241</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>18842</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19688</t>
+          <t>19130</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>12847</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31523</t>
+          <t>31481</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>20208</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24600</t>
+          <t>23829</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17610</t>
+          <t>17294</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>38875</t>
+          <t>37865</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39312</t>
+          <t>41533</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67312</t>
+          <t>68698</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30076</t>
+          <t>29702</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52582</t>
+          <t>53426</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>77080</t>
+          <t>77033</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>112051</t>
+          <t>113046</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>89284</t>
+          <t>88844</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124394</t>
+          <t>124668</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64483</t>
+          <t>64085</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>95275</t>
+          <t>94714</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>162900</t>
+          <t>162124</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>209131</t>
+          <t>211295</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>199533</t>
+          <t>198262</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>239229</t>
+          <t>238103</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>160506</t>
+          <t>163194</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>197319</t>
+          <t>197389</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>371572</t>
+          <t>367904</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>425866</t>
+          <t>423633</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,3%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>26995</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>52696</t>
+          <t>53451</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17794</t>
+          <t>18335</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39113</t>
+          <t>39168</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>50873</t>
+          <t>51436</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>83482</t>
+          <t>85397</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>59030</t>
+          <t>58090</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>97659</t>
+          <t>95612</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>59474</t>
+          <t>60045</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>91949</t>
+          <t>91511</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>127092</t>
+          <t>125572</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>175290</t>
+          <t>172949</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>255462</t>
+          <t>254758</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>318984</t>
+          <t>317637</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>162240</t>
+          <t>161096</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>209433</t>
+          <t>210266</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>434669</t>
+          <t>430047</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>508551</t>
+          <t>509790</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>346522</t>
+          <t>345810</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>417308</t>
+          <t>410788</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>265089</t>
+          <t>267257</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>324239</t>
+          <t>327275</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>622867</t>
+          <t>623586</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>713638</t>
+          <t>715936</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>602258</t>
+          <t>605890</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>680039</t>
+          <t>683259</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>429776</t>
+          <t>424681</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>492566</t>
+          <t>489448</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1053904</t>
+          <t>1048893</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1152704</t>
+          <t>1155843</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6714-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6714-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>14367</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>13286</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>13255</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20746</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>18883</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38642</t>
+          <t>39562</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>13516</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30930</t>
+          <t>30152</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>36856</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62478</t>
+          <t>63740</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55310</t>
+          <t>55438</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83777</t>
+          <t>83383</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37272</t>
+          <t>37060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61118</t>
+          <t>60369</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>98504</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>135616</t>
+          <t>136685</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>143796</t>
+          <t>144420</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176290</t>
+          <t>178655</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70687</t>
+          <t>71126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97204</t>
+          <t>98067</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>225478</t>
+          <t>224461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>266999</t>
+          <t>266183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,87%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12827</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20027</t>
+          <t>19221</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18230</t>
+          <t>18633</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12718</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33785</t>
+          <t>32607</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45711</t>
+          <t>45165</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75088</t>
+          <t>73768</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39945</t>
+          <t>40187</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67752</t>
+          <t>65954</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91083</t>
+          <t>91948</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131674</t>
+          <t>132771</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72325</t>
+          <t>71869</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106509</t>
+          <t>107876</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51285</t>
+          <t>49947</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80083</t>
+          <t>80202</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128678</t>
+          <t>134403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176343</t>
+          <t>178047</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>225462</t>
+          <t>224509</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>266445</t>
+          <t>267089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120069</t>
+          <t>123571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155742</t>
+          <t>157103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>359197</t>
+          <t>361274</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>414356</t>
+          <t>413684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,73%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11386</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16401</t>
+          <t>16599</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>28978</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26771</t>
+          <t>28599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22535</t>
+          <t>23085</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48503</t>
+          <t>48120</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29568</t>
+          <t>30159</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54107</t>
+          <t>54685</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44498</t>
+          <t>45051</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>57358</t>
+          <t>56425</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>89539</t>
+          <t>88754</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>38831</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68233</t>
+          <t>67945</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40028</t>
+          <t>37511</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66299</t>
+          <t>64255</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86773</t>
+          <t>86264</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>125465</t>
+          <t>125125</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>188353</t>
+          <t>186878</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222522</t>
+          <t>223856</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,49 +2562,49 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>58,51%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>70,08%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>109407</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>94371</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>125874</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>51,26%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>44,21%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>58,97%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>69,67%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>109407</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>94660</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>124691</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>51,26%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>44,35%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>58,42%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>287</t>
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>289790</t>
+          <t>290253</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>337886</t>
+          <t>338470</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,52%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13528</t>
+          <t>14483</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14269</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24090</t>
+          <t>23334</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10732</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27495</t>
+          <t>28076</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>14621</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16794</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36725</t>
+          <t>36192</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52948</t>
+          <t>52203</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>83811</t>
+          <t>83701</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36997</t>
+          <t>37157</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>66154</t>
+          <t>64604</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>96341</t>
+          <t>98282</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>137098</t>
+          <t>139735</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95572</t>
+          <t>94234</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>130272</t>
+          <t>131828</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61223</t>
+          <t>62414</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>91833</t>
+          <t>91922</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>164669</t>
+          <t>166999</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>212216</t>
+          <t>213331</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>194484</t>
+          <t>193953</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>235241</t>
+          <t>236133</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140944</t>
+          <t>141871</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>175510</t>
+          <t>176080</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>346342</t>
+          <t>345993</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>401999</t>
+          <t>399371</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>13742</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>33441</t>
+          <t>34170</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,82 +3474,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>17738</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>10488</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>27858</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>40287</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>30285</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>55743</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>2,36%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>17738</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>10896</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>28388</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>40287</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>28500</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>55319</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>37814</t>
+          <t>37009</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>66223</t>
+          <t>66184</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28133</t>
+          <t>28576</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55537</t>
+          <t>55752</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>72187</t>
+          <t>71279</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>113893</t>
+          <t>112385</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>168176</t>
+          <t>168757</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>221423</t>
+          <t>224994</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>133635</t>
+          <t>132604</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>177963</t>
+          <t>182021</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>314423</t>
+          <t>316369</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>388836</t>
+          <t>386894</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>291319</t>
+          <t>288603</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>359715</t>
+          <t>357218</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>213748</t>
+          <t>212703</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>267521</t>
+          <t>267655</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>520028</t>
+          <t>521384</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>605764</t>
+          <t>603596</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>788887</t>
+          <t>789635</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>865000</t>
+          <t>867498</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>460768</t>
+          <t>459151</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>524402</t>
+          <t>522657</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1268668</t>
+          <t>1272053</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1371607</t>
+          <t>1370481</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2470</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13774</t>
+          <t>13096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19329</t>
+          <t>19037</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11659</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27365</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>19265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21251</t>
+          <t>20986</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42886</t>
+          <t>41776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27577</t>
+          <t>28442</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51125</t>
+          <t>51943</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23516</t>
+          <t>23465</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43168</t>
+          <t>42353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56911</t>
+          <t>55860</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86618</t>
+          <t>86493</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61935</t>
+          <t>61436</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89370</t>
+          <t>89306</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47676</t>
+          <t>46091</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71903</t>
+          <t>69496</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115378</t>
+          <t>115064</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153241</t>
+          <t>154512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89760</t>
+          <t>89327</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>120080</t>
+          <t>120621</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48226</t>
+          <t>49804</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73392</t>
+          <t>73665</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146173</t>
+          <t>145579</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>185300</t>
+          <t>187138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16228</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22737</t>
+          <t>22930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23180</t>
+          <t>22875</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>11645</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30604</t>
+          <t>29177</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23500</t>
+          <t>23167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46345</t>
+          <t>46583</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64018</t>
+          <t>66309</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97267</t>
+          <t>98076</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34632</t>
+          <t>33799</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59345</t>
+          <t>59866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>106781</t>
+          <t>106697</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>148617</t>
+          <t>147115</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97159</t>
+          <t>94986</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133941</t>
+          <t>130858</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65503</t>
+          <t>67578</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97086</t>
+          <t>96069</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>170898</t>
+          <t>171529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>218328</t>
+          <t>217857</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,67%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>176538</t>
+          <t>178590</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>220303</t>
+          <t>217464</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>105523</t>
+          <t>105266</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138314</t>
+          <t>138050</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>291876</t>
+          <t>293233</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348490</t>
+          <t>347601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,54%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23088</t>
+          <t>23751</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>12518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31373</t>
+          <t>31085</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20448</t>
+          <t>20319</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43430</t>
+          <t>43949</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19361</t>
+          <t>19357</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39127</t>
+          <t>40210</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44157</t>
+          <t>44629</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73283</t>
+          <t>77572</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96544</t>
+          <t>95346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134484</t>
+          <t>133059</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53392</t>
+          <t>54231</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82239</t>
+          <t>83080</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>157347</t>
+          <t>155943</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>201658</t>
+          <t>204743</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66944</t>
+          <t>66784</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98314</t>
+          <t>98953</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59194</t>
+          <t>61003</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90268</t>
+          <t>89653</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135709</t>
+          <t>133883</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178317</t>
+          <t>181527</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>105640</t>
+          <t>105669</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>142148</t>
+          <t>143122</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>79466</t>
+          <t>78812</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111121</t>
+          <t>110125</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>195215</t>
+          <t>190949</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>244241</t>
+          <t>244509</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>19711</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19130</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>13802</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31481</t>
+          <t>33074</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23829</t>
+          <t>23326</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17294</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37865</t>
+          <t>37299</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41533</t>
+          <t>39026</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68698</t>
+          <t>67791</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29702</t>
+          <t>30485</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53426</t>
+          <t>53669</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>77033</t>
+          <t>77784</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>113046</t>
+          <t>112287</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88844</t>
+          <t>90043</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124668</t>
+          <t>125190</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64085</t>
+          <t>64520</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94714</t>
+          <t>96839</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>162124</t>
+          <t>159249</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>211295</t>
+          <t>209845</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>198262</t>
+          <t>199246</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>238103</t>
+          <t>239312</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,47 +6886,47 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>49,67%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>59,65%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>179546</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>160864</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>197572</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>55,16%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>49,42%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>59,35%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>179546</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>163194</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>197389</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>55,16%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>50,14%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>367904</t>
+          <t>373130</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>423633</t>
+          <t>427689</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,86%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26995</t>
+          <t>27060</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53451</t>
+          <t>53344</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18335</t>
+          <t>18019</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39168</t>
+          <t>39567</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>51436</t>
+          <t>51590</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>85397</t>
+          <t>85485</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>58090</t>
+          <t>58390</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>95612</t>
+          <t>93531</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>60045</t>
+          <t>59426</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>91511</t>
+          <t>92233</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>125572</t>
+          <t>127148</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>172949</t>
+          <t>175728</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>254758</t>
+          <t>257661</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>317637</t>
+          <t>319836</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>161096</t>
+          <t>160892</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>210266</t>
+          <t>210549</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>430047</t>
+          <t>430212</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>509790</t>
+          <t>514825</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>345810</t>
+          <t>346519</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>410788</t>
+          <t>415395</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>267257</t>
+          <t>264339</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>327275</t>
+          <t>323364</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>623586</t>
+          <t>624891</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>715936</t>
+          <t>712366</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>605890</t>
+          <t>607478</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>683259</t>
+          <t>686802</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>424681</t>
+          <t>425403</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>489448</t>
+          <t>490477</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1048893</t>
+          <t>1050849</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1155843</t>
+          <t>1150343</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
